--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4068C230-6D3C-4D97-A50E-46D64A34AA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A898B427-6A05-4073-85ED-EAF3630B1C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8523" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8524" uniqueCount="312">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -1454,9 +1454,8 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" t="str">
-        <f>IFERROR([1]Veda!D5,"ts_24c")</f>
-        <v>ts_24c</v>
+      <c r="A10" t="s">
+        <v>49</v>
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A898B427-6A05-4073-85ED-EAF3630B1C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B194ADD9-DB22-43A9-BED6-C2B964B053AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8524" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8552" uniqueCount="314">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -980,6 +980,12 @@
   <si>
     <t>hydro</t>
   </si>
+  <si>
+    <t>distr_*</t>
+  </si>
+  <si>
+    <t>ELC4H,ELC8H</t>
+  </si>
 </sst>
 </file>
 
@@ -35858,6 +35864,10 @@
       <c r="AA16">
         <v>0.72625641920235962</v>
       </c>
+      <c r="AC16" t="str">
+        <f>IF(A18="x","DeActivated","~TFM_INS-TSL: attribute=FLO_SHAR; limtype=FX; year=0")</f>
+        <v>~TFM_INS-TSL: attribute=FLO_SHAR; limtype=FX; year=0</v>
+      </c>
       <c r="CE16" t="s">
         <v>189</v>
       </c>
@@ -36013,6 +36023,84 @@
       <c r="AA17">
         <v>0.76439677311498799</v>
       </c>
+      <c r="AC17" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD17" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE17" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF17" t="s">
+        <v>57</v>
+      </c>
+      <c r="AG17" t="s">
+        <v>58</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>59</v>
+      </c>
+      <c r="AI17" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>62</v>
+      </c>
+      <c r="AL17" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>64</v>
+      </c>
+      <c r="AN17" t="s">
+        <v>65</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>66</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS17" t="s">
+        <v>70</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV17" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>74</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY17" t="s">
+        <v>76</v>
+      </c>
+      <c r="AZ17" t="s">
+        <v>77</v>
+      </c>
+      <c r="BA17" t="s">
+        <v>78</v>
+      </c>
+      <c r="BB17" t="s">
+        <v>79</v>
+      </c>
       <c r="CE17" t="s">
         <v>190</v>
       </c>
@@ -36167,6 +36255,84 @@
       </c>
       <c r="AA18">
         <v>0.74975218116134268</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>312</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>313</v>
+      </c>
+      <c r="AE18">
+        <v>3</v>
+      </c>
+      <c r="AF18">
+        <v>3</v>
+      </c>
+      <c r="AG18">
+        <v>3</v>
+      </c>
+      <c r="AH18">
+        <v>3</v>
+      </c>
+      <c r="AI18">
+        <v>3</v>
+      </c>
+      <c r="AJ18">
+        <v>3</v>
+      </c>
+      <c r="AK18">
+        <v>3</v>
+      </c>
+      <c r="AL18">
+        <v>3</v>
+      </c>
+      <c r="AM18">
+        <v>3</v>
+      </c>
+      <c r="AN18">
+        <v>3</v>
+      </c>
+      <c r="AO18">
+        <v>3</v>
+      </c>
+      <c r="AP18">
+        <v>3</v>
+      </c>
+      <c r="AQ18">
+        <v>3</v>
+      </c>
+      <c r="AR18">
+        <v>3</v>
+      </c>
+      <c r="AS18">
+        <v>3</v>
+      </c>
+      <c r="AT18">
+        <v>3</v>
+      </c>
+      <c r="AU18">
+        <v>3</v>
+      </c>
+      <c r="AV18">
+        <v>3</v>
+      </c>
+      <c r="AW18">
+        <v>3</v>
+      </c>
+      <c r="AX18">
+        <v>3</v>
+      </c>
+      <c r="AY18">
+        <v>3</v>
+      </c>
+      <c r="AZ18">
+        <v>3</v>
+      </c>
+      <c r="BA18">
+        <v>3</v>
+      </c>
+      <c r="BB18">
+        <v>3</v>
       </c>
       <c r="CE18" t="s">
         <v>191</v>

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B194ADD9-DB22-43A9-BED6-C2B964B053AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0784C82-FCA1-4CB5-B658-5E45148CC63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -1505,8 +1505,8 @@
     <row r="19" spans="3:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45"/>
     <row r="21" spans="3:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="H21" s="3" t="str">
-        <f>IF(H23=H24,"Not Required!","~UC_T: LO")</f>
-        <v>~UC_T: LO</v>
+        <f>IF(H23=H24,"Not Required!","~UC_T: N")</f>
+        <v>~UC_T: N</v>
       </c>
     </row>
     <row r="22" spans="3:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">

--- a/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SuppXLS/Scen_TSParameters_ts_24c.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78BAAF62-8160-45EB-877B-FD22F0FB7E6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0218E593-37FC-4559-9523-C643501A7E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8552" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8859" uniqueCount="315">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -927,9 +927,6 @@
     <t>other_indexes</t>
   </si>
   <si>
-    <t>ncap_com</t>
-  </si>
-  <si>
     <t>DEF_C</t>
   </si>
   <si>
@@ -985,6 +982,12 @@
   </si>
   <si>
     <t>~UC_T: LO~2035</t>
+  </si>
+  <si>
+    <t>~TFM_DINS-AT</t>
+  </si>
+  <si>
+    <t>NCAP_COM</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1468,7 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D10" t="s">
         <v>48</v>
@@ -1474,19 +1477,19 @@
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B11" s="5"/>
       <c r="C11" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D11" t="s">
         <v>300</v>
-      </c>
-      <c r="D11" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="D12" t="s">
         <v>302</v>
-      </c>
-      <c r="D12" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.45">
@@ -1601,7 +1604,7 @@
     </row>
     <row r="29" spans="3:14" ht="17.649999999999999" thickBot="1" x14ac:dyDescent="0.6">
       <c r="I29" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="3:14" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
@@ -34178,9 +34181,8 @@
         <f>IF(A11="x","DeActivated","~TFM_DINS-TSL: attribute=NCAP_PKCNT")</f>
         <v>~TFM_DINS-TSL: attribute=NCAP_PKCNT</v>
       </c>
-      <c r="DE9" t="str">
-        <f>IF(A11="x","DeActivated","~TFM_INS-AT")</f>
-        <v>~TFM_INS-AT</v>
+      <c r="DE9" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="2:112" x14ac:dyDescent="0.45">
@@ -34503,7 +34505,7 @@
         <v>293</v>
       </c>
       <c r="DH10" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="2:112" x14ac:dyDescent="0.45">
@@ -34817,16 +34819,16 @@
         <v>2.3954978897144093E-2</v>
       </c>
       <c r="DE11" t="s">
-        <v>288</v>
+        <v>183</v>
       </c>
       <c r="DF11" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG11" t="s">
         <v>295</v>
       </c>
-      <c r="DG11" t="s">
-        <v>296</v>
-      </c>
       <c r="DH11">
-        <v>0.23708793194680855</v>
+        <v>0.50370673847493896</v>
       </c>
     </row>
     <row r="12" spans="2:112" x14ac:dyDescent="0.45">
@@ -35140,16 +35142,16 @@
         <v>4.3397704651151552E-2</v>
       </c>
       <c r="DE12" t="s">
-        <v>290</v>
+        <v>184</v>
       </c>
       <c r="DF12" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG12" t="s">
         <v>295</v>
       </c>
-      <c r="DG12" t="s">
-        <v>296</v>
-      </c>
       <c r="DH12">
-        <v>0.23708793194680855</v>
+        <v>0.48302393451711439</v>
       </c>
     </row>
     <row r="13" spans="2:112" x14ac:dyDescent="0.45">
@@ -35463,16 +35465,16 @@
         <v>5.1254541203916315E-2</v>
       </c>
       <c r="DE13" t="s">
-        <v>291</v>
+        <v>185</v>
       </c>
       <c r="DF13" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG13" t="s">
         <v>295</v>
       </c>
-      <c r="DG13" t="s">
-        <v>296</v>
-      </c>
       <c r="DH13">
-        <v>0.23708793194680855</v>
+        <v>0.51376621200574313</v>
       </c>
     </row>
     <row r="14" spans="2:112" x14ac:dyDescent="0.45">
@@ -35629,6 +35631,18 @@
       <c r="DC14">
         <v>3.8671844445541642E-2</v>
       </c>
+      <c r="DE14" t="s">
+        <v>186</v>
+      </c>
+      <c r="DF14" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG14" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH14">
+        <v>0.47107272990405064</v>
+      </c>
     </row>
     <row r="15" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
@@ -35784,6 +35798,18 @@
       <c r="DC15">
         <v>2.9693889609546463E-2</v>
       </c>
+      <c r="DE15" t="s">
+        <v>187</v>
+      </c>
+      <c r="DF15" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG15" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH15">
+        <v>0.48723433708609165</v>
+      </c>
     </row>
     <row r="16" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
@@ -35943,8 +35969,20 @@
       <c r="DC16">
         <v>9.4507661159432182E-2</v>
       </c>
-    </row>
-    <row r="17" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE16" t="s">
+        <v>188</v>
+      </c>
+      <c r="DF16" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG16" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH16">
+        <v>0.54323106269455479</v>
+      </c>
+    </row>
+    <row r="17" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>189</v>
       </c>
@@ -36176,8 +36214,20 @@
       <c r="DC17">
         <v>7.8304493914972045E-2</v>
       </c>
-    </row>
-    <row r="18" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE17" t="s">
+        <v>189</v>
+      </c>
+      <c r="DF17" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG17" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH17">
+        <v>0.52556231967023592</v>
+      </c>
+    </row>
+    <row r="18" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>190</v>
       </c>
@@ -36257,10 +36307,10 @@
         <v>0.74975218116134268</v>
       </c>
       <c r="AC18" t="s">
+        <v>310</v>
+      </c>
+      <c r="AD18" t="s">
         <v>311</v>
-      </c>
-      <c r="AD18" t="s">
-        <v>312</v>
       </c>
       <c r="AE18">
         <v>3</v>
@@ -36409,8 +36459,20 @@
       <c r="DC18">
         <v>7.2122970342452089E-2</v>
       </c>
-    </row>
-    <row r="19" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE18" t="s">
+        <v>190</v>
+      </c>
+      <c r="DF18" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG18" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH18">
+        <v>0.52543987086589539</v>
+      </c>
+    </row>
+    <row r="19" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>191</v>
       </c>
@@ -36564,8 +36626,20 @@
       <c r="DC19">
         <v>6.9087121056125328E-2</v>
       </c>
-    </row>
-    <row r="20" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE19" t="s">
+        <v>191</v>
+      </c>
+      <c r="DF19" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG19" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH19">
+        <v>0.51646834033988476</v>
+      </c>
+    </row>
+    <row r="20" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>192</v>
       </c>
@@ -36719,8 +36793,20 @@
       <c r="DC20">
         <v>9.9761988572840937E-2</v>
       </c>
-    </row>
-    <row r="21" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE20" t="s">
+        <v>192</v>
+      </c>
+      <c r="DF20" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG20" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH20">
+        <v>0.51036124881305511</v>
+      </c>
+    </row>
+    <row r="21" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>193</v>
       </c>
@@ -36874,8 +36960,20 @@
       <c r="DC21">
         <v>8.7535604368242967E-2</v>
       </c>
-    </row>
-    <row r="22" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE21" t="s">
+        <v>193</v>
+      </c>
+      <c r="DF21" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG21" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH21">
+        <v>0.53356283907500324</v>
+      </c>
+    </row>
+    <row r="22" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>194</v>
       </c>
@@ -37029,8 +37127,20 @@
       <c r="DC22">
         <v>0.10812620042294009</v>
       </c>
-    </row>
-    <row r="23" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE22" t="s">
+        <v>194</v>
+      </c>
+      <c r="DF22" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG22" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH22">
+        <v>0.48643411818915605</v>
+      </c>
+    </row>
+    <row r="23" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>195</v>
       </c>
@@ -37184,8 +37294,20 @@
       <c r="DC23">
         <v>9.5725309846978746E-2</v>
       </c>
-    </row>
-    <row r="24" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE23" t="s">
+        <v>195</v>
+      </c>
+      <c r="DF23" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG23" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH23">
+        <v>0.51662520381395516</v>
+      </c>
+    </row>
+    <row r="24" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>196</v>
       </c>
@@ -37339,8 +37461,20 @@
       <c r="DC24">
         <v>0.11630881185875805</v>
       </c>
-    </row>
-    <row r="25" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE24" t="s">
+        <v>196</v>
+      </c>
+      <c r="DF24" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG24" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH24">
+        <v>0.51562899300500153</v>
+      </c>
+    </row>
+    <row r="25" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>197</v>
       </c>
@@ -37494,8 +37628,20 @@
       <c r="DC25">
         <v>3.5112609403200684E-2</v>
       </c>
-    </row>
-    <row r="26" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE25" t="s">
+        <v>197</v>
+      </c>
+      <c r="DF25" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG25" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH25">
+        <v>0.48080175524906837</v>
+      </c>
+    </row>
+    <row r="26" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>198</v>
       </c>
@@ -37649,8 +37795,20 @@
       <c r="DC26">
         <v>3.5392134784589427E-2</v>
       </c>
-    </row>
-    <row r="27" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE26" t="s">
+        <v>198</v>
+      </c>
+      <c r="DF26" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG26" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH26">
+        <v>0.47633101858230864</v>
+      </c>
+    </row>
+    <row r="27" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>199</v>
       </c>
@@ -37804,8 +37962,20 @@
       <c r="DC27">
         <v>4.6376561432655096E-2</v>
       </c>
-    </row>
-    <row r="28" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE27" t="s">
+        <v>199</v>
+      </c>
+      <c r="DF27" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG27" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH27">
+        <v>0.49326006330253419</v>
+      </c>
+    </row>
+    <row r="28" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>200</v>
       </c>
@@ -37959,8 +38129,20 @@
       <c r="DC28">
         <v>7.3103797379188568E-2</v>
       </c>
-    </row>
-    <row r="29" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE28" t="s">
+        <v>200</v>
+      </c>
+      <c r="DF28" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG28" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH28">
+        <v>0.51181453873051153</v>
+      </c>
+    </row>
+    <row r="29" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>201</v>
       </c>
@@ -38114,8 +38296,20 @@
       <c r="DC29">
         <v>6.6834825011324817E-2</v>
       </c>
-    </row>
-    <row r="30" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE29" t="s">
+        <v>201</v>
+      </c>
+      <c r="DF29" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG29" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH29">
+        <v>0.58310557804430863</v>
+      </c>
+    </row>
+    <row r="30" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>202</v>
       </c>
@@ -38269,8 +38463,20 @@
       <c r="DC30">
         <v>5.2999406433769686E-2</v>
       </c>
-    </row>
-    <row r="31" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE30" t="s">
+        <v>202</v>
+      </c>
+      <c r="DF30" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG30" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH30">
+        <v>0.53136084579222742</v>
+      </c>
+    </row>
+    <row r="31" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>203</v>
       </c>
@@ -38424,8 +38630,20 @@
       <c r="DC31">
         <v>6.637100906484604E-2</v>
       </c>
-    </row>
-    <row r="32" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE31" t="s">
+        <v>203</v>
+      </c>
+      <c r="DF31" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG31" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH31">
+        <v>0.50479833261506868</v>
+      </c>
+    </row>
+    <row r="32" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>204</v>
       </c>
@@ -38579,8 +38797,20 @@
       <c r="DC32">
         <v>6.9291438986905998E-2</v>
       </c>
-    </row>
-    <row r="33" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE32" t="s">
+        <v>204</v>
+      </c>
+      <c r="DF32" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG32" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH32">
+        <v>0.44648872094139613</v>
+      </c>
+    </row>
+    <row r="33" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>205</v>
       </c>
@@ -38734,8 +38964,20 @@
       <c r="DC33">
         <v>6.7578920753297883E-2</v>
       </c>
-    </row>
-    <row r="34" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE33" t="s">
+        <v>205</v>
+      </c>
+      <c r="DF33" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG33" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH33">
+        <v>0.43247109039991022</v>
+      </c>
+    </row>
+    <row r="34" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>206</v>
       </c>
@@ -38889,8 +39131,20 @@
       <c r="DC34">
         <v>7.30698142600128E-2</v>
       </c>
-    </row>
-    <row r="35" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE34" t="s">
+        <v>206</v>
+      </c>
+      <c r="DF34" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG34" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH34">
+        <v>0.46104061505161387</v>
+      </c>
+    </row>
+    <row r="35" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>207</v>
       </c>
@@ -39044,8 +39298,20 @@
       <c r="DC35">
         <v>8.0917120259599198E-2</v>
       </c>
-    </row>
-    <row r="36" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE35" t="s">
+        <v>207</v>
+      </c>
+      <c r="DF35" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG35" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH35">
+        <v>0.47932732899115887</v>
+      </c>
+    </row>
+    <row r="36" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>208</v>
       </c>
@@ -39199,8 +39465,20 @@
       <c r="DC36">
         <v>8.4245000969396314E-2</v>
       </c>
-    </row>
-    <row r="37" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE36" t="s">
+        <v>208</v>
+      </c>
+      <c r="DF36" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG36" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH36">
+        <v>0.51169108973005017</v>
+      </c>
+    </row>
+    <row r="37" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>209</v>
       </c>
@@ -39354,8 +39632,20 @@
       <c r="DC37">
         <v>8.3159817846127373E-2</v>
       </c>
-    </row>
-    <row r="38" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE37" t="s">
+        <v>209</v>
+      </c>
+      <c r="DF37" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG37" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH37">
+        <v>0.48306029940771417</v>
+      </c>
+    </row>
+    <row r="38" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>210</v>
       </c>
@@ -39509,8 +39799,20 @@
       <c r="DC38">
         <v>6.5942047750329191E-2</v>
       </c>
-    </row>
-    <row r="39" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE38" t="s">
+        <v>210</v>
+      </c>
+      <c r="DF38" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG38" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH38">
+        <v>0.44760387525760803</v>
+      </c>
+    </row>
+    <row r="39" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>211</v>
       </c>
@@ -39664,8 +39966,20 @@
       <c r="DC39">
         <v>7.2911843016718519E-2</v>
       </c>
-    </row>
-    <row r="40" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE39" t="s">
+        <v>211</v>
+      </c>
+      <c r="DF39" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG39" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH39">
+        <v>0.45364490455231571</v>
+      </c>
+    </row>
+    <row r="40" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
         <v>212</v>
       </c>
@@ -39819,8 +40133,20 @@
       <c r="DC40">
         <v>7.1499220478822817E-2</v>
       </c>
-    </row>
-    <row r="41" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE40" t="s">
+        <v>212</v>
+      </c>
+      <c r="DF40" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG40" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH40">
+        <v>0.45316207747718079</v>
+      </c>
+    </row>
+    <row r="41" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
         <v>213</v>
       </c>
@@ -39974,8 +40300,20 @@
       <c r="DC41">
         <v>6.3180163260211086E-2</v>
       </c>
-    </row>
-    <row r="42" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE41" t="s">
+        <v>213</v>
+      </c>
+      <c r="DF41" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG41" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH41">
+        <v>0.4015226031704261</v>
+      </c>
+    </row>
+    <row r="42" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
         <v>214</v>
       </c>
@@ -40129,8 +40467,20 @@
       <c r="DC42">
         <v>7.118433099824438E-2</v>
       </c>
-    </row>
-    <row r="43" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE42" t="s">
+        <v>214</v>
+      </c>
+      <c r="DF42" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG42" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH42">
+        <v>0.43883058873330927</v>
+      </c>
+    </row>
+    <row r="43" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
         <v>215</v>
       </c>
@@ -40284,8 +40634,20 @@
       <c r="DC43">
         <v>9.3210533467607867E-2</v>
       </c>
-    </row>
-    <row r="44" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE43" t="s">
+        <v>215</v>
+      </c>
+      <c r="DF43" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG43" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH43">
+        <v>0.48032486611766234</v>
+      </c>
+    </row>
+    <row r="44" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
         <v>216</v>
       </c>
@@ -40439,8 +40801,20 @@
       <c r="DC44">
         <v>0.10254495088368269</v>
       </c>
-    </row>
-    <row r="45" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE44" t="s">
+        <v>216</v>
+      </c>
+      <c r="DF44" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG44" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH44">
+        <v>0.51156901027736257</v>
+      </c>
+    </row>
+    <row r="45" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
         <v>217</v>
       </c>
@@ -40594,8 +40968,20 @@
       <c r="DC45">
         <v>0.14792655730938675</v>
       </c>
-    </row>
-    <row r="46" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE45" t="s">
+        <v>217</v>
+      </c>
+      <c r="DF45" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG45" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH45">
+        <v>0.46696380793470704</v>
+      </c>
+    </row>
+    <row r="46" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
         <v>218</v>
       </c>
@@ -40749,8 +41135,20 @@
       <c r="DC46">
         <v>0.13168796342638997</v>
       </c>
-    </row>
-    <row r="47" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE46" t="s">
+        <v>218</v>
+      </c>
+      <c r="DF46" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG46" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH46">
+        <v>0.48961705341132611</v>
+      </c>
+    </row>
+    <row r="47" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
         <v>219</v>
       </c>
@@ -40904,8 +41302,20 @@
       <c r="DC47">
         <v>0.10106783763123151</v>
       </c>
-    </row>
-    <row r="48" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE47" t="s">
+        <v>219</v>
+      </c>
+      <c r="DF47" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG47" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH47">
+        <v>0.52256705930936809</v>
+      </c>
+    </row>
+    <row r="48" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
         <v>220</v>
       </c>
@@ -41059,8 +41469,20 @@
       <c r="DC48">
         <v>0.10338077129002415</v>
       </c>
-    </row>
-    <row r="49" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE48" t="s">
+        <v>220</v>
+      </c>
+      <c r="DF48" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG48" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH48">
+        <v>0.52730891502111743</v>
+      </c>
+    </row>
+    <row r="49" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
         <v>221</v>
       </c>
@@ -41214,8 +41636,20 @@
       <c r="DC49">
         <v>9.1514783093218366E-2</v>
       </c>
-    </row>
-    <row r="50" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE49" t="s">
+        <v>221</v>
+      </c>
+      <c r="DF49" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG49" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH49">
+        <v>0.54016293347762545</v>
+      </c>
+    </row>
+    <row r="50" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
         <v>222</v>
       </c>
@@ -41369,8 +41803,20 @@
       <c r="DC50">
         <v>8.9339686797674733E-2</v>
       </c>
-    </row>
-    <row r="51" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE50" t="s">
+        <v>222</v>
+      </c>
+      <c r="DF50" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG50" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH50">
+        <v>0.53589718944133791</v>
+      </c>
+    </row>
+    <row r="51" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
         <v>223</v>
       </c>
@@ -41524,8 +41970,20 @@
       <c r="DC51">
         <v>0.14503175548151789</v>
       </c>
-    </row>
-    <row r="52" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE51" t="s">
+        <v>223</v>
+      </c>
+      <c r="DF51" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG51" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH51">
+        <v>0.54682362188447331</v>
+      </c>
+    </row>
+    <row r="52" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
         <v>224</v>
       </c>
@@ -41679,8 +42137,20 @@
       <c r="DC52">
         <v>0.11795451643136447</v>
       </c>
-    </row>
-    <row r="53" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE52" t="s">
+        <v>224</v>
+      </c>
+      <c r="DF52" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG52" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH52">
+        <v>0.54800149760800432</v>
+      </c>
+    </row>
+    <row r="53" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
         <v>225</v>
       </c>
@@ -41834,8 +42304,20 @@
       <c r="DC53">
         <v>0.10402913364789033</v>
       </c>
-    </row>
-    <row r="54" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE53" t="s">
+        <v>225</v>
+      </c>
+      <c r="DF53" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG53" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH53">
+        <v>0.5192743644979988</v>
+      </c>
+    </row>
+    <row r="54" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
         <v>226</v>
       </c>
@@ -41989,8 +42471,20 @@
       <c r="DC54">
         <v>0.59920195040128788</v>
       </c>
-    </row>
-    <row r="55" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE54" t="s">
+        <v>246</v>
+      </c>
+      <c r="DF54" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG54" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH54">
+        <v>0.42614323559179129</v>
+      </c>
+    </row>
+    <row r="55" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
         <v>227</v>
       </c>
@@ -42144,8 +42638,20 @@
       <c r="DC55">
         <v>0.60583095904688244</v>
       </c>
-    </row>
-    <row r="56" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE55" t="s">
+        <v>247</v>
+      </c>
+      <c r="DF55" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG55" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH55">
+        <v>0.48978786649246525</v>
+      </c>
+    </row>
+    <row r="56" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
         <v>228</v>
       </c>
@@ -42299,8 +42805,20 @@
       <c r="DC56">
         <v>0.53570245025164287</v>
       </c>
-    </row>
-    <row r="57" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE56" t="s">
+        <v>248</v>
+      </c>
+      <c r="DF56" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG56" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH56">
+        <v>0.27506464799902264</v>
+      </c>
+    </row>
+    <row r="57" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
         <v>229</v>
       </c>
@@ -42454,8 +42972,20 @@
       <c r="DC57">
         <v>0.62932435027412625</v>
       </c>
-    </row>
-    <row r="58" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE57" t="s">
+        <v>249</v>
+      </c>
+      <c r="DF57" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG57" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH57">
+        <v>0.282669596989434</v>
+      </c>
+    </row>
+    <row r="58" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
         <v>230</v>
       </c>
@@ -42609,8 +43139,20 @@
       <c r="DC58">
         <v>0.55383553604146596</v>
       </c>
-    </row>
-    <row r="59" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE58" t="s">
+        <v>250</v>
+      </c>
+      <c r="DF58" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG58" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH58">
+        <v>0.43914250767887925</v>
+      </c>
+    </row>
+    <row r="59" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
         <v>231</v>
       </c>
@@ -42764,8 +43306,20 @@
       <c r="DC59">
         <v>0.64057251070078058</v>
       </c>
-    </row>
-    <row r="60" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE59" t="s">
+        <v>251</v>
+      </c>
+      <c r="DF59" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG59" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH59">
+        <v>0.46410162703749064</v>
+      </c>
+    </row>
+    <row r="60" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
         <v>232</v>
       </c>
@@ -42919,8 +43473,20 @@
       <c r="DC60">
         <v>0.50016799012232283</v>
       </c>
-    </row>
-    <row r="61" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE60" t="s">
+        <v>252</v>
+      </c>
+      <c r="DF60" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG60" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH60">
+        <v>0.2831504670254073</v>
+      </c>
+    </row>
+    <row r="61" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
         <v>233</v>
       </c>
@@ -43074,8 +43640,20 @@
       <c r="DC61">
         <v>0.46593687117526983</v>
       </c>
-    </row>
-    <row r="62" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE61" t="s">
+        <v>253</v>
+      </c>
+      <c r="DF61" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG61" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH61">
+        <v>0.32173043883697838</v>
+      </c>
+    </row>
+    <row r="62" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
         <v>234</v>
       </c>
@@ -43229,8 +43807,20 @@
       <c r="DC62">
         <v>0.45580812326855785</v>
       </c>
-    </row>
-    <row r="63" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE62" t="s">
+        <v>254</v>
+      </c>
+      <c r="DF62" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG62" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH62">
+        <v>0.30853933855824739</v>
+      </c>
+    </row>
+    <row r="63" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
         <v>235</v>
       </c>
@@ -43384,8 +43974,20 @@
       <c r="DC63">
         <v>0.5751426225149554</v>
       </c>
-    </row>
-    <row r="64" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE63" t="s">
+        <v>255</v>
+      </c>
+      <c r="DF63" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG63" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH63">
+        <v>0.20050086272324566</v>
+      </c>
+    </row>
+    <row r="64" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
         <v>236</v>
       </c>
@@ -43539,8 +44141,20 @@
       <c r="DC64">
         <v>0.65739203988332795</v>
       </c>
-    </row>
-    <row r="65" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE64" t="s">
+        <v>256</v>
+      </c>
+      <c r="DF64" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG64" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH64">
+        <v>0.24372073715694195</v>
+      </c>
+    </row>
+    <row r="65" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
         <v>237</v>
       </c>
@@ -43694,8 +44308,20 @@
       <c r="DC65">
         <v>0.60353446594483895</v>
       </c>
-    </row>
-    <row r="66" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE65" t="s">
+        <v>257</v>
+      </c>
+      <c r="DF65" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG65" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH65">
+        <v>0.37125724383844977</v>
+      </c>
+    </row>
+    <row r="66" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
         <v>238</v>
       </c>
@@ -43849,8 +44475,20 @@
       <c r="DC66">
         <v>0.58689101134125565</v>
       </c>
-    </row>
-    <row r="67" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE66" t="s">
+        <v>258</v>
+      </c>
+      <c r="DF66" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG66" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH66">
+        <v>0.44250323010849452</v>
+      </c>
+    </row>
+    <row r="67" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
         <v>239</v>
       </c>
@@ -44004,8 +44642,20 @@
       <c r="DC67">
         <v>0.59291198663152755</v>
       </c>
-    </row>
-    <row r="68" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE67" t="s">
+        <v>259</v>
+      </c>
+      <c r="DF67" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG67" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH67">
+        <v>0.3596875593320103</v>
+      </c>
+    </row>
+    <row r="68" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
         <v>240</v>
       </c>
@@ -44159,8 +44809,20 @@
       <c r="DC68">
         <v>0.43946329098519854</v>
       </c>
-    </row>
-    <row r="69" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE68" t="s">
+        <v>260</v>
+      </c>
+      <c r="DF68" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG68" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH68">
+        <v>0.23058139452249615</v>
+      </c>
+    </row>
+    <row r="69" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
         <v>241</v>
       </c>
@@ -44314,8 +44976,20 @@
       <c r="DC69">
         <v>0.60186569720857686</v>
       </c>
-    </row>
-    <row r="70" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE69" t="s">
+        <v>261</v>
+      </c>
+      <c r="DF69" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG69" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH69">
+        <v>0.40479273378684821</v>
+      </c>
+    </row>
+    <row r="70" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
         <v>242</v>
       </c>
@@ -44469,8 +45143,20 @@
       <c r="DC70">
         <v>0.5202547944263809</v>
       </c>
-    </row>
-    <row r="71" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE70" t="s">
+        <v>262</v>
+      </c>
+      <c r="DF70" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG70" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH70">
+        <v>0.19895335600565139</v>
+      </c>
+    </row>
+    <row r="71" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
         <v>243</v>
       </c>
@@ -44624,8 +45310,20 @@
       <c r="DC71">
         <v>0.48671316965545852</v>
       </c>
-    </row>
-    <row r="72" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE71" t="s">
+        <v>263</v>
+      </c>
+      <c r="DF71" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG71" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH71">
+        <v>0.47624250251711625</v>
+      </c>
+    </row>
+    <row r="72" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
         <v>244</v>
       </c>
@@ -44779,8 +45477,20 @@
       <c r="DC72">
         <v>0.51477808800545322</v>
       </c>
-    </row>
-    <row r="73" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE72" t="s">
+        <v>264</v>
+      </c>
+      <c r="DF72" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG72" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH72">
+        <v>0.2621386356531088</v>
+      </c>
+    </row>
+    <row r="73" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
         <v>245</v>
       </c>
@@ -44934,8 +45644,20 @@
       <c r="DC73">
         <v>0.31831638993363159</v>
       </c>
-    </row>
-    <row r="74" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE73" t="s">
+        <v>265</v>
+      </c>
+      <c r="DF73" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG73" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH73">
+        <v>0.27362925177304237</v>
+      </c>
+    </row>
+    <row r="74" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
         <v>246</v>
       </c>
@@ -45089,8 +45811,20 @@
       <c r="DC74">
         <v>0.21581131864600969</v>
       </c>
-    </row>
-    <row r="75" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE74" t="s">
+        <v>266</v>
+      </c>
+      <c r="DF74" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG74" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH74">
+        <v>0.3166603908389175</v>
+      </c>
+    </row>
+    <row r="75" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
         <v>247</v>
       </c>
@@ -45244,8 +45978,20 @@
       <c r="DC75">
         <v>0.31514877880358255</v>
       </c>
-    </row>
-    <row r="76" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE75" t="s">
+        <v>267</v>
+      </c>
+      <c r="DF75" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG75" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH75">
+        <v>0.26179276133504081</v>
+      </c>
+    </row>
+    <row r="76" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
         <v>248</v>
       </c>
@@ -45399,8 +46145,20 @@
       <c r="DC76">
         <v>0.18310467680498083</v>
       </c>
-    </row>
-    <row r="77" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE76" t="s">
+        <v>268</v>
+      </c>
+      <c r="DF76" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG76" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH76">
+        <v>0.37673749082307378</v>
+      </c>
+    </row>
+    <row r="77" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
         <v>249</v>
       </c>
@@ -45554,8 +46312,20 @@
       <c r="DC77">
         <v>0.16099901001608119</v>
       </c>
-    </row>
-    <row r="78" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE77" t="s">
+        <v>269</v>
+      </c>
+      <c r="DF77" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG77" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH77">
+        <v>0.41983809919099274</v>
+      </c>
+    </row>
+    <row r="78" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
         <v>250</v>
       </c>
@@ -45709,8 +46479,20 @@
       <c r="DC78">
         <v>0.34756329331352731</v>
       </c>
-    </row>
-    <row r="79" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE78" t="s">
+        <v>270</v>
+      </c>
+      <c r="DF78" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG78" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH78">
+        <v>0.25372688959541306</v>
+      </c>
+    </row>
+    <row r="79" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
         <v>251</v>
       </c>
@@ -45864,8 +46646,20 @@
       <c r="DC79">
         <v>0.39745929085260762</v>
       </c>
-    </row>
-    <row r="80" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE79" t="s">
+        <v>271</v>
+      </c>
+      <c r="DF79" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG79" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH79">
+        <v>0.22618110674883452</v>
+      </c>
+    </row>
+    <row r="80" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
         <v>252</v>
       </c>
@@ -46019,8 +46813,20 @@
       <c r="DC80">
         <v>9.7063425402581921E-2</v>
       </c>
-    </row>
-    <row r="81" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE80" t="s">
+        <v>272</v>
+      </c>
+      <c r="DF80" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG80" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH80">
+        <v>0.38288647247102869</v>
+      </c>
+    </row>
+    <row r="81" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
         <v>253</v>
       </c>
@@ -46174,8 +46980,20 @@
       <c r="DC81">
         <v>0.28587577919808593</v>
       </c>
-    </row>
-    <row r="82" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE81" t="s">
+        <v>273</v>
+      </c>
+      <c r="DF81" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG81" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH81">
+        <v>0.37207599417815362</v>
+      </c>
+    </row>
+    <row r="82" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
         <v>254</v>
       </c>
@@ -46329,8 +47147,20 @@
       <c r="DC82">
         <v>0.30516526368051605</v>
       </c>
-    </row>
-    <row r="83" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE82" t="s">
+        <v>274</v>
+      </c>
+      <c r="DF82" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG82" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH82">
+        <v>0.38120468597388968</v>
+      </c>
+    </row>
+    <row r="83" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
         <v>255</v>
       </c>
@@ -46484,8 +47314,20 @@
       <c r="DC83">
         <v>0.1932748284703617</v>
       </c>
-    </row>
-    <row r="84" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE83" t="s">
+        <v>275</v>
+      </c>
+      <c r="DF83" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG83" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH83">
+        <v>0.337373498924393</v>
+      </c>
+    </row>
+    <row r="84" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
         <v>256</v>
       </c>
@@ -46639,8 +47481,20 @@
       <c r="DC84">
         <v>0.27753552794623126</v>
       </c>
-    </row>
-    <row r="85" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE84" t="s">
+        <v>276</v>
+      </c>
+      <c r="DF84" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG84" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH84">
+        <v>0.37037704267484411</v>
+      </c>
+    </row>
+    <row r="85" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
         <v>257</v>
       </c>
@@ -46794,8 +47648,20 @@
       <c r="DC85">
         <v>0.33780751925001934</v>
       </c>
-    </row>
-    <row r="86" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE85" t="s">
+        <v>277</v>
+      </c>
+      <c r="DF85" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG85" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH85">
+        <v>0.43700465119201382</v>
+      </c>
+    </row>
+    <row r="86" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
         <v>258</v>
       </c>
@@ -46949,8 +47815,20 @@
       <c r="DC86">
         <v>0.35273354003159862</v>
       </c>
-    </row>
-    <row r="87" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE86" t="s">
+        <v>278</v>
+      </c>
+      <c r="DF86" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG86" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH86">
+        <v>0.46508418165940996</v>
+      </c>
+    </row>
+    <row r="87" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
         <v>259</v>
       </c>
@@ -47104,8 +47982,20 @@
       <c r="DC87">
         <v>0.20638819715305076</v>
       </c>
-    </row>
-    <row r="88" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE87" t="s">
+        <v>279</v>
+      </c>
+      <c r="DF87" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG87" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH87">
+        <v>0.35759748456423252</v>
+      </c>
+    </row>
+    <row r="88" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
         <v>260</v>
       </c>
@@ -47259,8 +48149,20 @@
       <c r="DC88">
         <v>0.24617431215072375</v>
       </c>
-    </row>
-    <row r="89" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE88" t="s">
+        <v>280</v>
+      </c>
+      <c r="DF88" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG88" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH88">
+        <v>0.60464824337471434</v>
+      </c>
+    </row>
+    <row r="89" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
         <v>261</v>
       </c>
@@ -47414,8 +48316,20 @@
       <c r="DC89">
         <v>0.41417032767237888</v>
       </c>
-    </row>
-    <row r="90" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE89" t="s">
+        <v>281</v>
+      </c>
+      <c r="DF89" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG89" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH89">
+        <v>0.56951376647228602</v>
+      </c>
+    </row>
+    <row r="90" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
         <v>262</v>
       </c>
@@ -47569,8 +48483,20 @@
       <c r="DC90">
         <v>0.12847001553811427</v>
       </c>
-    </row>
-    <row r="91" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE90" t="s">
+        <v>282</v>
+      </c>
+      <c r="DF90" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG90" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH90">
+        <v>0.41873568479699952</v>
+      </c>
+    </row>
+    <row r="91" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
         <v>263</v>
       </c>
@@ -47724,8 +48650,20 @@
       <c r="DC91">
         <v>0.4149333563956033</v>
       </c>
-    </row>
-    <row r="92" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE91" t="s">
+        <v>283</v>
+      </c>
+      <c r="DF91" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG91" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH91">
+        <v>0.37123451024463433</v>
+      </c>
+    </row>
+    <row r="92" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
         <v>264</v>
       </c>
@@ -47879,8 +48817,20 @@
       <c r="DC92">
         <v>0.21574009180092399</v>
       </c>
-    </row>
-    <row r="93" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE92" t="s">
+        <v>284</v>
+      </c>
+      <c r="DF92" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG92" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH92">
+        <v>0.52721309535301841</v>
+      </c>
+    </row>
+    <row r="93" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
         <v>265</v>
       </c>
@@ -48034,8 +48984,20 @@
       <c r="DC93">
         <v>0.29794921203898578</v>
       </c>
-    </row>
-    <row r="94" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE93" t="s">
+        <v>285</v>
+      </c>
+      <c r="DF93" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG93" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH93">
+        <v>0.4648982676357567</v>
+      </c>
+    </row>
+    <row r="94" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
         <v>266</v>
       </c>
@@ -48189,8 +49151,20 @@
       <c r="DC94">
         <v>0.36530845228995223</v>
       </c>
-    </row>
-    <row r="95" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE94" t="s">
+        <v>286</v>
+      </c>
+      <c r="DF94" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG94" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH94">
+        <v>0.50507041203019476</v>
+      </c>
+    </row>
+    <row r="95" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
         <v>267</v>
       </c>
@@ -48344,8 +49318,20 @@
       <c r="DC95">
         <v>0.26337412194485621</v>
       </c>
-    </row>
-    <row r="96" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE95" t="s">
+        <v>287</v>
+      </c>
+      <c r="DF95" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG95" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH95">
+        <v>0.47940255316647984</v>
+      </c>
+    </row>
+    <row r="96" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
         <v>268</v>
       </c>
@@ -48499,8 +49485,20 @@
       <c r="DC96">
         <v>0.37052140846908255</v>
       </c>
-    </row>
-    <row r="97" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE96" t="s">
+        <v>226</v>
+      </c>
+      <c r="DF96" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG96" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH96">
+        <v>0.71115262678378899</v>
+      </c>
+    </row>
+    <row r="97" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
         <v>269</v>
       </c>
@@ -48654,8 +49652,20 @@
       <c r="DC97">
         <v>0.26943742340522203</v>
       </c>
-    </row>
-    <row r="98" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE97" t="s">
+        <v>227</v>
+      </c>
+      <c r="DF97" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG97" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH97">
+        <v>0.74338080172493415</v>
+      </c>
+    </row>
+    <row r="98" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
         <v>270</v>
       </c>
@@ -48809,8 +49819,20 @@
       <c r="DC98">
         <v>0.20605730711950609</v>
       </c>
-    </row>
-    <row r="99" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE98" t="s">
+        <v>228</v>
+      </c>
+      <c r="DF98" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG98" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH98">
+        <v>0.65421738559584985</v>
+      </c>
+    </row>
+    <row r="99" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
         <v>271</v>
       </c>
@@ -48964,8 +49986,20 @@
       <c r="DC99">
         <v>0.17486333136664209</v>
       </c>
-    </row>
-    <row r="100" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE99" t="s">
+        <v>229</v>
+      </c>
+      <c r="DF99" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG99" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH99">
+        <v>0.75095474966398668</v>
+      </c>
+    </row>
+    <row r="100" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
         <v>272</v>
       </c>
@@ -49119,8 +50153,20 @@
       <c r="DC100">
         <v>0.26532884961380582</v>
       </c>
-    </row>
-    <row r="101" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE100" t="s">
+        <v>230</v>
+      </c>
+      <c r="DF100" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG100" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH100">
+        <v>0.60590037790416384</v>
+      </c>
+    </row>
+    <row r="101" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
         <v>273</v>
       </c>
@@ -49274,8 +50320,20 @@
       <c r="DC101">
         <v>0.27579905854354719</v>
       </c>
-    </row>
-    <row r="102" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE101" t="s">
+        <v>231</v>
+      </c>
+      <c r="DF101" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG101" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH101">
+        <v>0.69893328918860043</v>
+      </c>
+    </row>
+    <row r="102" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
         <v>274</v>
       </c>
@@ -49429,8 +50487,20 @@
       <c r="DC102">
         <v>0.36544875602787846</v>
       </c>
-    </row>
-    <row r="103" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE102" t="s">
+        <v>232</v>
+      </c>
+      <c r="DF102" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG102" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH102">
+        <v>0.5451853628875869</v>
+      </c>
+    </row>
+    <row r="103" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
         <v>275</v>
       </c>
@@ -49584,8 +50654,20 @@
       <c r="DC103">
         <v>0.30816900520422963</v>
       </c>
-    </row>
-    <row r="104" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE103" t="s">
+        <v>233</v>
+      </c>
+      <c r="DF103" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG103" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH103">
+        <v>0.4831660681681747</v>
+      </c>
+    </row>
+    <row r="104" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
         <v>276</v>
       </c>
@@ -49739,8 +50821,20 @@
       <c r="DC104">
         <v>0.32721901599041942</v>
       </c>
-    </row>
-    <row r="105" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE104" t="s">
+        <v>234</v>
+      </c>
+      <c r="DF104" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG104" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH104">
+        <v>0.52172811296076194</v>
+      </c>
+    </row>
+    <row r="105" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
         <v>277</v>
       </c>
@@ -49894,8 +50988,20 @@
       <c r="DC105">
         <v>0.33480545164023884</v>
       </c>
-    </row>
-    <row r="106" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE105" t="s">
+        <v>235</v>
+      </c>
+      <c r="DF105" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG105" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH105">
+        <v>0.5166195719848099</v>
+      </c>
+    </row>
+    <row r="106" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
         <v>278</v>
       </c>
@@ -50049,8 +51155,20 @@
       <c r="DC106">
         <v>0.37087078637226861</v>
       </c>
-    </row>
-    <row r="107" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE106" t="s">
+        <v>236</v>
+      </c>
+      <c r="DF106" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG106" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH106">
+        <v>0.64780804961726879</v>
+      </c>
+    </row>
+    <row r="107" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
         <v>279</v>
       </c>
@@ -50204,8 +51322,20 @@
       <c r="DC107">
         <v>0.31235959972838467</v>
       </c>
-    </row>
-    <row r="108" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE107" t="s">
+        <v>237</v>
+      </c>
+      <c r="DF107" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG107" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH107">
+        <v>0.59806374230134574</v>
+      </c>
+    </row>
+    <row r="108" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
         <v>280</v>
       </c>
@@ -50359,8 +51489,20 @@
       <c r="DC108">
         <v>0.52114362613621712</v>
       </c>
-    </row>
-    <row r="109" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE108" t="s">
+        <v>238</v>
+      </c>
+      <c r="DF108" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG108" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH108">
+        <v>0.62592879524539102</v>
+      </c>
+    </row>
+    <row r="109" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
         <v>281</v>
       </c>
@@ -50514,8 +51656,20 @@
       <c r="DC109">
         <v>0.49207636653971654</v>
       </c>
-    </row>
-    <row r="110" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE109" t="s">
+        <v>239</v>
+      </c>
+      <c r="DF109" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG109" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH109">
+        <v>0.61968614506308606</v>
+      </c>
+    </row>
+    <row r="110" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
         <v>282</v>
       </c>
@@ -50669,8 +51823,20 @@
       <c r="DC110">
         <v>0.31361460353031706</v>
       </c>
-    </row>
-    <row r="111" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE110" t="s">
+        <v>240</v>
+      </c>
+      <c r="DF110" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG110" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH110">
+        <v>0.47519476972031616</v>
+      </c>
+    </row>
+    <row r="111" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
         <v>283</v>
       </c>
@@ -50824,8 +51990,20 @@
       <c r="DC111">
         <v>0.30018775467607162</v>
       </c>
-    </row>
-    <row r="112" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE111" t="s">
+        <v>241</v>
+      </c>
+      <c r="DF111" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG111" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH111">
+        <v>0.59288429629678296</v>
+      </c>
+    </row>
+    <row r="112" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
         <v>284</v>
       </c>
@@ -50979,8 +52157,20 @@
       <c r="DC112">
         <v>0.50512673735572211</v>
       </c>
-    </row>
-    <row r="113" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE112" t="s">
+        <v>242</v>
+      </c>
+      <c r="DF112" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG112" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH112">
+        <v>0.55935852472416725</v>
+      </c>
+    </row>
+    <row r="113" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
         <v>285</v>
       </c>
@@ -51134,8 +52324,20 @@
       <c r="DC113">
         <v>0.45054822033637687</v>
       </c>
-    </row>
-    <row r="114" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE113" t="s">
+        <v>243</v>
+      </c>
+      <c r="DF113" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG113" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH113">
+        <v>0.51379875832839927</v>
+      </c>
+    </row>
+    <row r="114" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
         <v>286</v>
       </c>
@@ -51289,8 +52491,20 @@
       <c r="DC114">
         <v>0.37615150204852771</v>
       </c>
-    </row>
-    <row r="115" spans="2:107" x14ac:dyDescent="0.45">
+      <c r="DE114" t="s">
+        <v>244</v>
+      </c>
+      <c r="DF114" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG114" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH114">
+        <v>0.52106244503473365</v>
+      </c>
+    </row>
+    <row r="115" spans="2:112" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
         <v>287</v>
       </c>
@@ -51443,6 +52657,18 @@
       </c>
       <c r="DC115">
         <v>0.34660465121100337</v>
+      </c>
+      <c r="DE115" t="s">
+        <v>245</v>
+      </c>
+      <c r="DF115" t="s">
+        <v>294</v>
+      </c>
+      <c r="DG115" t="s">
+        <v>295</v>
+      </c>
+      <c r="DH115">
+        <v>0.35647557686852005</v>
       </c>
     </row>
   </sheetData>
@@ -51463,7 +52689,7 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
@@ -51486,7 +52712,7 @@
         <v>54</v>
       </c>
       <c r="E11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
@@ -51500,7 +52726,7 @@
         <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
@@ -51514,7 +52740,7 @@
         <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -51528,7 +52754,7 @@
         <v>58</v>
       </c>
       <c r="E14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
@@ -51542,7 +52768,7 @@
         <v>59</v>
       </c>
       <c r="E15" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
@@ -51556,7 +52782,7 @@
         <v>60</v>
       </c>
       <c r="E16" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
@@ -51570,7 +52796,7 @@
         <v>61</v>
       </c>
       <c r="E17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
@@ -51584,7 +52810,7 @@
         <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
@@ -51598,7 +52824,7 @@
         <v>63</v>
       </c>
       <c r="E19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
@@ -51612,7 +52838,7 @@
         <v>64</v>
       </c>
       <c r="E20" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
@@ -51626,7 +52852,7 @@
         <v>65</v>
       </c>
       <c r="E21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
@@ -51640,7 +52866,7 @@
         <v>66</v>
       </c>
       <c r="E22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
@@ -51654,7 +52880,7 @@
         <v>67</v>
       </c>
       <c r="E23" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
@@ -51668,7 +52894,7 @@
         <v>68</v>
       </c>
       <c r="E24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
@@ -51682,7 +52908,7 @@
         <v>69</v>
       </c>
       <c r="E25" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
@@ -51696,7 +52922,7 @@
         <v>70</v>
       </c>
       <c r="E26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
@@ -51710,7 +52936,7 @@
         <v>71</v>
       </c>
       <c r="E27" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
@@ -51724,7 +52950,7 @@
         <v>72</v>
       </c>
       <c r="E28" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
@@ -51738,7 +52964,7 @@
         <v>73</v>
       </c>
       <c r="E29" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
@@ -51752,7 +52978,7 @@
         <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
@@ -51766,7 +52992,7 @@
         <v>75</v>
       </c>
       <c r="E31" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
@@ -51780,7 +53006,7 @@
         <v>76</v>
       </c>
       <c r="E32" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
@@ -51794,7 +53020,7 @@
         <v>77</v>
       </c>
       <c r="E33" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
@@ -51808,7 +53034,7 @@
         <v>78</v>
       </c>
       <c r="E34" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -51840,7 +53066,7 @@
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C11" t="s">
         <v>54</v>
@@ -51851,7 +53077,7 @@
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C12" t="s">
         <v>56</v>
@@ -51862,7 +53088,7 @@
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C13" t="s">
         <v>57</v>
@@ -51873,7 +53099,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C14" t="s">
         <v>58</v>
@@ -51884,7 +53110,7 @@
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C15" t="s">
         <v>59</v>
@@ -51895,7 +53121,7 @@
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C16" t="s">
         <v>60</v>
@@ -51906,7 +53132,7 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C17" t="s">
         <v>61</v>
@@ -51917,7 +53143,7 @@
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C18" t="s">
         <v>62</v>
@@ -51928,7 +53154,7 @@
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C19" t="s">
         <v>63</v>
@@ -51939,7 +53165,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C20" t="s">
         <v>64</v>
@@ -51950,7 +53176,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C21" t="s">
         <v>65</v>
@@ -51961,7 +53187,7 @@
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C22" t="s">
         <v>66</v>
@@ -51972,7 +53198,7 @@
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C23" t="s">
         <v>67</v>
@@ -51983,7 +53209,7 @@
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
@@ -51994,7 +53220,7 @@
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C25" t="s">
         <v>69</v>
@@ -52005,7 +53231,7 @@
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C26" t="s">
         <v>70</v>
@@ -52016,7 +53242,7 @@
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C27" t="s">
         <v>71</v>
@@ -52027,7 +53253,7 @@
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C28" t="s">
         <v>72</v>
@@ -52038,7 +53264,7 @@
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C29" t="s">
         <v>73</v>
@@ -52049,7 +53275,7 @@
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C30" t="s">
         <v>74</v>
@@ -52060,7 +53286,7 @@
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C31" t="s">
         <v>75</v>
@@ -52071,7 +53297,7 @@
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C32" t="s">
         <v>76</v>
@@ -52082,7 +53308,7 @@
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C33" t="s">
         <v>77</v>
@@ -52093,7 +53319,7 @@
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C34" t="s">
         <v>78</v>
@@ -52104,7 +53330,7 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C35" t="s">
         <v>54</v>
@@ -52115,7 +53341,7 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C36" t="s">
         <v>56</v>
@@ -52126,7 +53352,7 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C37" t="s">
         <v>57</v>
@@ -52137,7 +53363,7 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C38" t="s">
         <v>58</v>
@@ -52148,7 +53374,7 @@
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C39" t="s">
         <v>59</v>
@@ -52159,7 +53385,7 @@
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C40" t="s">
         <v>60</v>
@@ -52170,7 +53396,7 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C41" t="s">
         <v>61</v>
@@ -52181,7 +53407,7 @@
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C42" t="s">
         <v>62</v>
@@ -52192,7 +53418,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C43" t="s">
         <v>63</v>
@@ -52203,7 +53429,7 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C44" t="s">
         <v>64</v>
@@ -52214,7 +53440,7 @@
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C45" t="s">
         <v>65</v>
@@ -52225,7 +53451,7 @@
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C46" t="s">
         <v>66</v>
@@ -52236,7 +53462,7 @@
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C47" t="s">
         <v>67</v>
@@ -52247,7 +53473,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C48" t="s">
         <v>68</v>
@@ -52258,7 +53484,7 @@
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C49" t="s">
         <v>69</v>
@@ -52269,7 +53495,7 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C50" t="s">
         <v>70</v>
@@ -52280,7 +53506,7 @@
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C51" t="s">
         <v>71</v>
@@ -52291,7 +53517,7 @@
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C52" t="s">
         <v>72</v>
@@ -52302,7 +53528,7 @@
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C53" t="s">
         <v>73</v>
@@ -52313,7 +53539,7 @@
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C54" t="s">
         <v>74</v>
@@ -52324,7 +53550,7 @@
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C55" t="s">
         <v>75</v>
@@ -52335,7 +53561,7 @@
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C56" t="s">
         <v>76</v>
@@ -52346,7 +53572,7 @@
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C57" t="s">
         <v>77</v>
@@ -52357,7 +53583,7 @@
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C58" t="s">
         <v>78</v>
@@ -52390,7 +53616,7 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.45">
@@ -52675,16 +53901,16 @@
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C10" t="s">
         <v>50</v>
       </c>
       <c r="D10" t="s">
+        <v>307</v>
+      </c>
+      <c r="E10" t="s">
         <v>308</v>
-      </c>
-      <c r="E10" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
@@ -52698,7 +53924,7 @@
         <v>0.11636666666666666</v>
       </c>
       <c r="E11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
@@ -52712,7 +53938,7 @@
         <v>0.14516666666666664</v>
       </c>
       <c r="E12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
@@ -52726,7 +53952,7 @@
         <v>7.8466666666666671E-2</v>
       </c>
       <c r="E13" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
@@ -52740,7 +53966,7 @@
         <v>0.11586666666666667</v>
       </c>
       <c r="E14" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
@@ -52754,7 +53980,7 @@
         <v>0.63963333333333339</v>
       </c>
       <c r="E15" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
@@ -52768,7 +53994,7 @@
         <v>0.15053333333333332</v>
       </c>
       <c r="E16" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.45">
@@ -52782,7 +54008,7 @@
         <v>6.6333333333333341E-2</v>
       </c>
       <c r="E17" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.45">
@@ -52796,7 +54022,7 @@
         <v>0.11586666666666667</v>
       </c>
       <c r="E18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.45">
@@ -52810,7 +54036,7 @@
         <v>0.73326666666666662</v>
       </c>
       <c r="E19" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.45">
@@ -52824,7 +54050,7 @@
         <v>0.71346666666666669</v>
       </c>
       <c r="E20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.45">
@@ -52838,7 +54064,7 @@
         <v>0.1762</v>
       </c>
       <c r="E21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
@@ -52852,7 +54078,7 @@
         <v>0.28870000000000001</v>
       </c>
       <c r="E22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
@@ -52866,7 +54092,7 @@
         <v>0.31186666666666668</v>
       </c>
       <c r="E23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
@@ -52880,7 +54106,7 @@
         <v>0.36856666666666671</v>
       </c>
       <c r="E24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
@@ -52894,7 +54120,7 @@
         <v>0.17863333333333334</v>
       </c>
       <c r="E25" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
@@ -52908,7 +54134,7 @@
         <v>0.11036666666666667</v>
       </c>
       <c r="E26" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
@@ -52922,7 +54148,7 @@
         <v>0.32233333333333331</v>
       </c>
       <c r="E27" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
@@ -52936,7 +54162,7 @@
         <v>0.32803333333333334</v>
       </c>
       <c r="E28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
@@ -52950,7 +54176,7 @@
         <v>0.19226666666666667</v>
       </c>
       <c r="E29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
@@ -52964,7 +54190,7 @@
         <v>0.20336666666666667</v>
       </c>
       <c r="E30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.45">
@@ -52978,7 +54204,7 @@
         <v>0.34349999999999997</v>
       </c>
       <c r="E31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.45">
@@ -52992,7 +54218,7 @@
         <v>0.20443333333333333</v>
       </c>
       <c r="E32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.45">
@@ -53006,7 +54232,7 @@
         <v>0.11793333333333333</v>
       </c>
       <c r="E33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.45">
@@ -53020,7 +54246,7 @@
         <v>6.4100000000000004E-2</v>
       </c>
       <c r="E34" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.45">
@@ -53034,7 +54260,7 @@
         <v>0.2733666666666667</v>
       </c>
       <c r="E35" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.45">
@@ -53048,7 +54274,7 @@
         <v>0.37426666666666669</v>
       </c>
       <c r="E36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.45">
@@ -53062,7 +54288,7 @@
         <v>0.13460000000000003</v>
       </c>
       <c r="E37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.45">
@@ -53076,7 +54302,7 @@
         <v>0.12383333333333334</v>
       </c>
       <c r="E38" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.45">
@@ -53090,7 +54316,7 @@
         <v>0.30443333333333333</v>
       </c>
       <c r="E39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.45">
@@ -53104,7 +54330,7 @@
         <v>0.24256666666666668</v>
       </c>
       <c r="E40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.45">
@@ -53118,7 +54344,7 @@
         <v>0.11596666666666666</v>
       </c>
       <c r="E41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.45">
@@ -53132,7 +54358,7 @@
         <v>0.20236666666666669</v>
       </c>
       <c r="E42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.45">
@@ -53146,7 +54372,7 @@
         <v>0.39450000000000002</v>
       </c>
       <c r="E43" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.45">
@@ -53160,7 +54386,7 @@
         <v>0.27323333333333333</v>
       </c>
       <c r="E44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.45">
@@ -53174,7 +54400,7 @@
         <v>6.9066666666666665E-2</v>
       </c>
       <c r="E45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.45">
@@ -53188,7 +54414,7 @@
         <v>0.21983333333333333</v>
       </c>
       <c r="E46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.45">
@@ -53202,7 +54428,7 @@
         <v>0.37340000000000001</v>
       </c>
       <c r="E47" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.45">
@@ -53216,7 +54442,7 @@
         <v>0.23273333333333335</v>
       </c>
       <c r="E48" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.45">
@@ -53230,7 +54456,7 @@
         <v>7.9899999999999999E-2</v>
       </c>
       <c r="E49" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.45">
@@ -53244,7 +54470,7 @@
         <v>0.23929999999999998</v>
       </c>
       <c r="E50" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.45">
@@ -53258,7 +54484,7 @@
         <v>0.42853333333333338</v>
       </c>
       <c r="E51" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.45">
@@ -53272,7 +54498,7 @@
         <v>0.3887666666666667</v>
       </c>
       <c r="E52" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.45">
@@ -53286,7 +54512,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E53" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.45">
@@ -53300,7 +54526,7 @@
         <v>0.13006666666666666</v>
       </c>
       <c r="E54" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.45">
@@ -53314,7 +54540,7 @@
         <v>0.51756666666666662</v>
       </c>
       <c r="E55" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.45">
@@ -53328,7 +54554,7 @@
         <v>0.37013333333333337</v>
       </c>
       <c r="E56" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.45">
@@ -53342,7 +54568,7 @@
         <v>0.26600000000000001</v>
       </c>
       <c r="E57" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.45">
@@ -53356,7 +54582,7 @@
         <v>0.25193333333333334</v>
       </c>
       <c r="E58" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.45">
@@ -53370,7 +54596,7 @@
         <v>0.29743333333333338</v>
       </c>
       <c r="E59" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.45">
@@ -53384,7 +54610,7 @@
         <v>0.38219999999999993</v>
       </c>
       <c r="E60" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.45">
@@ -53398,7 +54624,7 @@
         <v>0.26449999999999996</v>
       </c>
       <c r="E61" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.45">
@@ -53412,7 +54638,7 @@
         <v>0.20803333333333332</v>
       </c>
       <c r="E62" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.45">
@@ -53426,7 +54652,7 @@
         <v>0.40710000000000002</v>
       </c>
       <c r="E63" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.45">
@@ -53440,7 +54666,7 @@
         <v>0.29320000000000002</v>
       </c>
       <c r="E64" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.45">
@@ -53454,7 +54680,7 @@
         <v>0.22930000000000003</v>
       </c>
       <c r="E65" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.45">
@@ -53468,7 +54694,7 @@
         <v>0.1929666666666667</v>
       </c>
       <c r="E66" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.45">
@@ -53482,7 +54708,7 @@
         <v>0.4432666666666667</v>
       </c>
       <c r="E67" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.45">
@@ -53496,7 +54722,7 @@
         <v>0.37166666666666659</v>
       </c>
       <c r="E68" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.45">
@@ -53510,7 +54736,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E69" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.45">
@@ -53524,7 +54750,7 @@
         <v>5.4733333333333335E-2</v>
       </c>
       <c r="E70" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.45">
@@ -53538,7 +54764,7 @@
         <v>0.42709999999999998</v>
       </c>
       <c r="E71" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.45">
@@ -53552,7 +54778,7 @@
         <v>0.16690000000000002</v>
       </c>
       <c r="E72" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.45">
@@ -53566,7 +54792,7 @@
         <v>0.16340000000000002</v>
       </c>
       <c r="E73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.45">
@@ -53580,7 +54806,7 @@
         <v>0.11470000000000001</v>
       </c>
       <c r="E74" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.45">
@@ -53594,7 +54820,7 @@
         <v>0.25393333333333334</v>
       </c>
       <c r="E75" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.45">
@@ -53608,7 +54834,7 @@
         <v>0.33733333333333332</v>
       </c>
       <c r="E76" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.45">
@@ -53622,7 +54848,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E77" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.45">
@@ -53636,7 +54862,7 @@
         <v>0.13589999999999999</v>
       </c>
       <c r="E78" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.45">
@@ -53650,7 +54876,7 @@
         <v>0.29016666666666663</v>
       </c>
       <c r="E79" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.45">
@@ -53664,7 +54890,7 @@
         <v>0.34273333333333333</v>
       </c>
       <c r="E80" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.45">
@@ -53678,7 +54904,7 @@
         <v>0.11126666666666667</v>
       </c>
       <c r="E81" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="82" spans="2:5" x14ac:dyDescent="0.45">
@@ -53692,7 +54918,7 @@
         <v>0.10056666666666665</v>
       </c>
       <c r="E82" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="83" spans="2:5" x14ac:dyDescent="0.45">
@@ -53706,7 +54932,7 @@
         <v>0.37720000000000004</v>
       </c>
       <c r="E83" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="84" spans="2:5" x14ac:dyDescent="0.45">
@@ -53720,7 +54946,7 @@
         <v>0.3926</v>
       </c>
       <c r="E84" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="85" spans="2:5" x14ac:dyDescent="0.45">
@@ -53734,7 +54960,7 @@
         <v>0.1704</v>
       </c>
       <c r="E85" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="2:5" x14ac:dyDescent="0.45">
@@ -53748,7 +54974,7 @@
         <v>0.20269999999999999</v>
       </c>
       <c r="E86" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="87" spans="2:5" x14ac:dyDescent="0.45">
@@ -53762,7 +54988,7 @@
         <v>0.26273333333333332</v>
       </c>
       <c r="E87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="88" spans="2:5" x14ac:dyDescent="0.45">
@@ -53776,7 +55002,7 @@
         <v>0.31196666666666667</v>
       </c>
       <c r="E88" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="89" spans="2:5" x14ac:dyDescent="0.45">
@@ -53790,7 +55016,7 @@
         <v>0.12449999999999999</v>
       </c>
       <c r="E89" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
@@ -53804,7 +55030,7 @@
         <v>0.22923333333333332</v>
       </c>
       <c r="E90" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
@@ -53818,7 +55044,7 @@
         <v>0.28789999999999999</v>
       </c>
       <c r="E91" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
@@ -53832,7 +55058,7 @@
         <v>0.28363333333333335</v>
       </c>
       <c r="E92" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="93" spans="2:5" x14ac:dyDescent="0.45">
@@ -53846,7 +55072,7 @@
         <v>8.4766666666666657E-2</v>
       </c>
       <c r="E93" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
@@ -53860,7 +55086,7 @@
         <v>0.23056666666666667</v>
       </c>
       <c r="E94" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
@@ -53874,7 +55100,7 @@
         <v>0.33876666666666666</v>
       </c>
       <c r="E95" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" spans="2:5" x14ac:dyDescent="0.45">
@@ -53888,7 +55114,7 @@
         <v>0.40140000000000003</v>
       </c>
       <c r="E96" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.45">
@@ -53902,7 +55128,7 @@
         <v>0.10609999999999999</v>
       </c>
       <c r="E97" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="98" spans="2:5" x14ac:dyDescent="0.45">
@@ -53916,7 +55142,7 @@
         <v>0.12146666666666667</v>
       </c>
       <c r="E98" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.45">
@@ -53930,7 +55156,7 @@
         <v>0.29856666666666665</v>
       </c>
       <c r="E99" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.45">
@@ -53944,7 +55170,7 @@
         <v>0.12736666666666666</v>
       </c>
       <c r="E100" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="101" spans="2:5" x14ac:dyDescent="0.45">
@@ -53958,7 +55184,7 @@
         <v>0.20493333333333333</v>
       </c>
       <c r="E101" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="102" spans="2:5" x14ac:dyDescent="0.45">
@@ -53972,7 +55198,7 @@
         <v>0.18963333333333335</v>
       </c>
       <c r="E102" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.45">
@@ -53986,7 +55212,7 @@
         <v>0.36143333333333327</v>
       </c>
       <c r="E103" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.45">
@@ -54000,7 +55226,7 @@
         <v>0.34583333333333338</v>
       </c>
       <c r="E104" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.45">
@@ -54014,7 +55240,7 @@
         <v>0.24406666666666665</v>
       </c>
       <c r="E105" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.45">
@@ -54028,7 +55254,7 @@
         <v>0.12663333333333335</v>
       </c>
       <c r="E106" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.45">
@@ -54042,7 +55268,7 @@
         <v>0.44693333333333335</v>
       </c>
       <c r="E107" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="108" spans="2:5" x14ac:dyDescent="0.45">
@@ -54056,7 +55282,7 @@
         <v>0.47516666666666668</v>
       </c>
       <c r="E108" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.45">
@@ -54070,7 +55296,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E109" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.45">
@@ -54084,7 +55310,7 @@
         <v>5.3266666666666664E-2</v>
       </c>
       <c r="E110" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.45">
@@ -54098,7 +55324,7 @@
         <v>0.47343333333333337</v>
       </c>
       <c r="E111" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.45">
@@ -54112,7 +55338,7 @@
         <v>0.43723333333333336</v>
       </c>
       <c r="E112" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.45">
@@ -54126,7 +55352,7 @@
         <v>0.16533333333333333</v>
       </c>
       <c r="E113" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="114" spans="2:5" x14ac:dyDescent="0.45">
@@ -54140,7 +55366,7 @@
         <v>0.23139999999999997</v>
       </c>
       <c r="E114" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="115" spans="2:5" x14ac:dyDescent="0.45">
@@ -54154,7 +55380,7 @@
         <v>0.32290000000000002</v>
       </c>
       <c r="E115" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.45">
@@ -54168,7 +55394,7 @@
         <v>0.37293333333333334</v>
       </c>
       <c r="E116" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.45">
@@ -54182,7 +55408,7 @@
         <v>0.29363333333333336</v>
       </c>
       <c r="E117" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.45">
@@ -54196,7 +55422,7 @@
         <v>0.14543333333333333</v>
       </c>
       <c r="E118" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="119" spans="2:5" x14ac:dyDescent="0.45">
@@ -54210,7 +55436,7 @@
         <v>0.39063333333333333</v>
       </c>
       <c r="E119" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="120" spans="2:5" x14ac:dyDescent="0.45">
@@ -54224,7 +55450,7 @@
         <v>0.12093333333333334</v>
       </c>
       <c r="E120" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="121" spans="2:5" x14ac:dyDescent="0.45">
@@ -54238,7 +55464,7 @@
         <v>9.8299999999999998E-2</v>
       </c>
       <c r="E121" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="122" spans="2:5" x14ac:dyDescent="0.45">
@@ -54252,7 +55478,7 @@
         <v>5.000000000000001E-2</v>
       </c>
       <c r="E122" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="123" spans="2:5" x14ac:dyDescent="0.45">
@@ -54266,7 +55492,7 @@
         <v>0.34403333333333336</v>
       </c>
       <c r="E123" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="124" spans="2:5" x14ac:dyDescent="0.45">
@@ -54280,7 +55506,7 @@
         <v>0.27913333333333329</v>
       </c>
       <c r="E124" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="125" spans="2:5" x14ac:dyDescent="0.45">
@@ -54294,7 +55520,7 @@
         <v>0.23246666666666668</v>
       </c>
       <c r="E125" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="126" spans="2:5" x14ac:dyDescent="0.45">
@@ -54308,7 +55534,7 @@
         <v>0.14909999999999998</v>
       </c>
       <c r="E126" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
